--- a/astro-site/public/dl/kit-tareas-pasteleria/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/BONUS-02-calendario-anual-tareas.xlsx
@@ -1,16 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calendario Anual" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Calendario Anual'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -119,49 +121,49 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -523,13 +525,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B7"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -537,6 +540,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -565,8 +569,16 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -575,17 +587,17 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="18"/>
-    <col customWidth="1" max="3" min="3" width="25"/>
-    <col customWidth="1" max="4" min="4" width="40"/>
-    <col customWidth="1" max="5" min="5" width="15"/>
-    <col customWidth="1" max="6" min="6" width="30"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -595,6 +607,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -923,7 +936,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>25 Nov</t>
+          <t>Último viernes de nov. (variable)</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1171,6 +1184,7 @@
         </is>
       </c>
     </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="16" t="inlineStr">
         <is>
@@ -1182,6 +1196,15 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/BONUS-02-calendario-anual-tareas.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/BONUS-02-calendario-anual-tareas.xlsx
@@ -77,7 +77,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -94,6 +94,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="00E8F5E9"/>
         <bgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -159,6 +164,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -525,7 +533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -558,21 +566,29 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>▸ Añade las fechas locales de tu zona (fiestas patronales, ferias)</t>
+          <t>▸ Anota en la columna verde «Fecha de este año» el día en que caen Semana Santa, el Día de la Madre, las comuniones y el Black Friday</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>▸ Añade las fechas locales de tu zona (fiestas patronales, ferias)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="3" t="inlineStr">
+        <is>
           <t>▸ Usa como base para planificar compras y producción extra</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+    <row r="9"/>
+    <row r="10">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -589,15 +605,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="40" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -621,564 +638,552 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
+          <t>Fecha de este año</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
           <t>Evento</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Producción Especial</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Antelación</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="A4" s="6" t="n">
+        <v>1</v>
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
           <t>6 Enero</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Día de Reyes</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>Roscón de Reyes (nata, trufa, crema)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F4" s="10" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Pico máximo del año para pastelerías</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="A5" s="6" t="n">
+        <v>2</v>
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
           <t>14 Febrero</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>San Valentín</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Tartas corazón, bombones, macarons rosas</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F5" s="10" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t>Packaging especial, mensajes personalizados</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="A6" s="6" t="n">
+        <v>3</v>
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
           <t>19 Marzo</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Día del Padre</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Tartas temáticas, pasteles de chocolate</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-      <c r="F6" s="10" t="inlineStr">
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t>Segundo pico fuerte del Q1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="A7" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Mar-Abr</t>
-        </is>
-      </c>
-      <c r="C7" s="8" t="inlineStr">
+          <t>Mar-Abr (variable)</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="8" t="inlineStr">
         <is>
           <t>Semana Santa</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>Torrijas, monas de Pascua, huevos chocolate</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>3 semanas</t>
         </is>
       </c>
-      <c r="F7" s="10" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t>Producción intensiva 7-10 días</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="A8" s="6" t="n">
+        <v>5</v>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>1er dom. Mayo</t>
-        </is>
-      </c>
-      <c r="C8" s="8" t="inlineStr">
+          <t>1er dom. de mayo (variable)</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Día de la Madre</t>
         </is>
       </c>
-      <c r="D8" s="9" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>Tartas con dedicatoria, ramos de macarons</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F8" s="10" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Pico muy fuerte — reforzar despacho</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="A9" s="6" t="n">
+        <v>6</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Junio</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="inlineStr">
+          <t>Abr-Jun (variable)</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="n"/>
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>Comuniones</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>Tartas personalizadas, candy bars, galletas decoradas</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>4-5 meses (catálogo en enero)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Pedidos con mucha antelación → 06 Eventos y Festivos · hoja Comuniones (Abr-Jun)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Jun-Sep</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>Temporada Verano</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>Helados artesanos, tartas frías, granizados</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>4 semanas</t>
         </is>
       </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>Pedidos con mucha antelación</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Jun-Sep</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Temporada Verano</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Helados artesanos, tartas frías, granizados</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>4 semanas</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Adaptar vitrina a productos fríos</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
+      <c r="A11" s="6" t="n">
+        <v>8</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
           <t>31 Octubre</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="17" t="n"/>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>Halloween</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>Galletas decoradas, cupcakes temáticos, tartas terror</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F11" s="10" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Decoración de escaparate</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
+      <c r="A12" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
           <t>1 Noviembre</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Todos los Santos</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
+      <c r="E12" s="9" t="inlineStr">
         <is>
           <t>Buñuelos de viento, huesos de santo, panellets</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F12" s="10" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Muy fuerte en zonas tradicionales</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
+      <c r="A13" s="6" t="n">
+        <v>10</v>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Último viernes de nov. (variable)</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>Black Friday</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>Promociones en lotes, cajas regalo descuento</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-      <c r="F13" s="10" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Oportunidad de venta online</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
+      <c r="A14" s="6" t="n">
+        <v>11</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Diciembre</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="17" t="n"/>
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Navidad Completa</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Turrones, polvorones, troncos, mazapanes</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t>6 semanas</t>
         </is>
       </c>
-      <c r="F14" s="10" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Mayor temporada — planificar personal extra</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
+      <c r="A15" s="6" t="n">
+        <v>12</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
           <t>31 Diciembre</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>Nochevieja</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="E15" s="9" t="inlineStr">
         <is>
           <t>Tartas para cena, petit fours, macarons</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>1 semana</t>
         </is>
       </c>
-      <c r="F15" s="10" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Pedidos de restaurantes</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
+      <c r="A16" s="11" t="n">
+        <v>13</v>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Fiestas Locales</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Dulces tradicionales de tu zona</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="F16" s="11" t="inlineStr">
         <is>
           <t>3 semanas</t>
         </is>
       </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
         <is>
           <t>AÑADE TUS FECHAS LOCALES</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+      <c r="A17" s="6" t="n">
+        <v>14</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="8" t="inlineStr">
         <is>
           <t>Bodas (temporada)</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="E17" s="9" t="inlineStr">
         <is>
           <t>Tartas nupciales, candy bars, detalles invitados</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>2-3 meses</t>
         </is>
       </c>
-      <c r="F17" s="10" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t>Abril-Octubre pico de bodas</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+      <c r="A18" s="6" t="n">
+        <v>15</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Eventos Corporativos</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="E18" s="9" t="inlineStr">
         <is>
           <t>Desayunos empresa, coffee break, cajas regalo</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>2 semanas</t>
         </is>
       </c>
-      <c r="F18" s="10" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>Todo el año, pico en Navidad</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
+      <c r="A19" s="6" t="n">
+        <v>16</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>Cumpleaños</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="E19" s="9" t="inlineStr">
         <is>
           <t>Tartas personalizadas por encargo</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>3-7 días</t>
         </is>
       </c>
-      <c r="F19" s="10" t="inlineStr">
+      <c r="G19" s="10" t="inlineStr">
         <is>
           <t>Ingresos constantes todo el año</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
+      <c r="A20" s="6" t="n">
+        <v>17</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Variable</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Bautizos/Comuniones/Aniversarios</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
+      <c r="E20" s="9" t="inlineStr">
         <is>
           <t>Tartas temáticas, galletas personalizadas</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>3-4 semanas</t>
         </is>
       </c>
-      <c r="F20" s="10" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>Fichas de pedido detalladas</t>
         </is>
@@ -1194,7 +1199,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
